--- a/Boletim-estruturado.xlsx
+++ b/Boletim-estruturado.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Dados" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Dados!$A$1:$T$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Dados!$A$1:$W$9</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,18 +24,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="76">
   <si>
     <t xml:space="preserve">BOLETIM DE APONTAMENTOS</t>
   </si>
   <si>
-    <t xml:space="preserve">1 apontamento(s) · origem: a0ca4a16-Apontamentos_8.xlsx · emitido em 26/08/2026 13:33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INCM-SIH-2026.00044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sinalização Horizontal   |   14/08/2026   |   Executado</t>
+    <t xml:space="preserve">1 apontamento(s) · 268,32 m² · 513,6 m · período 10/07/2026 a 10/07/2026 · origem: e89ee564-Apontamentos_4.xlsx · emitido em 26/08/2026 13:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INCM-SIH-2026.00026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sinalização Horizontal · Definitiva   |   10/07/2026   |   Executado</t>
   </si>
   <si>
     <t xml:space="preserve">IDENTIFICAÇÃO</t>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">CLIENTE</t>
   </si>
   <si>
-    <t xml:space="preserve">MOTIVA</t>
+    <t xml:space="preserve">EPR</t>
   </si>
   <si>
     <t xml:space="preserve">CONTRATO</t>
@@ -53,138 +53,138 @@
     <t xml:space="preserve">LOCAL DE OBRA</t>
   </si>
   <si>
-    <t xml:space="preserve">PR - 445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KM DO SERVIÇO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64+800</t>
+    <t xml:space="preserve">Maringá a Paiçandu</t>
   </si>
   <si>
     <t xml:space="preserve">ENCARREGADO</t>
   </si>
   <si>
-    <t xml:space="preserve">Vanderlei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EQUIPE</t>
+    <t xml:space="preserve">Fabiano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXECUTADO EM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/07/2026 09:58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENCONTRADO EM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECHAMENTO DE PISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIBERAÇÃO DE PISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMPO DE INTERDIÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGENHEIRO RESPONSÁVEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRIADO POR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabiano Martins · 10/07/2026 17:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EQUIPE (KARTADO)</t>
   </si>
   <si>
     <t xml:space="preserve">Fiscal de campo</t>
   </si>
   <si>
-    <t xml:space="preserve">EXECUTADO EM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/08/2026 10:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENCONTRADO EM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/08/2026 10:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRIADO POR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabriel Santos · 14/08/2026 15:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENGENHEIRO RESPONSÁVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FECHAMENTO DE PISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIBERAÇÃO DE PISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERVIÇO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITEM DE SERVIÇO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ensaio Retrô. - Fotoluminescente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIPO DE SERVIÇO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manutenção</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SENTIDO DE SERVIÇO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decrescente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEITURAS (10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÉDIA</t>
+    <t xml:space="preserve">SERVIÇOS EXECUTADOS (8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KM INI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KM FIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOCAL DE APLICAÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIPO DE FAIXA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAIXAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXTENSÃO (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LARGURA (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÁREA (m²)</t>
   </si>
   <si>
     <t xml:space="preserve">OBSERVAÇÕES</t>
   </si>
   <si>
-    <t xml:space="preserve">B.D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 foto(s) anexada(s) no apontamento</t>
+    <t xml:space="preserve">Branco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zebrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legendas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legenda de a preferência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Seta pé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Seta reta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 foto(s) anexada(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Serial</t>
   </si>
   <si>
+    <t xml:space="preserve">Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hora</t>
+  </si>
+  <si>
     <t xml:space="preserve">Natureza</t>
   </si>
   <si>
+    <t xml:space="preserve">Tipo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Status</t>
   </si>
   <si>
-    <t xml:space="preserve">Data de execução</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hora</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cliente</t>
   </si>
   <si>
@@ -197,64 +197,72 @@
     <t xml:space="preserve">Encarregado</t>
   </si>
   <si>
-    <t xml:space="preserve">Equipe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engenheiro responsável</t>
+    <t xml:space="preserve">Engenheiro</t>
   </si>
   <si>
     <t xml:space="preserve">Criado por</t>
   </si>
   <si>
-    <t xml:space="preserve">Km do serviço</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item de Serviço</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipo de Serviço - Lev. de Retrorrefletância</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sentido de Serviço</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Média de Leituras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observações</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leituras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fotos</t>
+    <t xml:space="preserve">Serviço nº</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Km inicial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Km final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local de aplicação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo de faixa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faixas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extensão (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Largura (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Área (m²)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obs. do serviço</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:58</t>
   </si>
   <si>
     <t xml:space="preserve">Sinalização Horizontal</t>
   </si>
   <si>
+    <t xml:space="preserve">Definitiva</t>
+  </si>
+  <si>
     <t xml:space="preserve">Executado</t>
   </si>
   <si>
-    <t xml:space="preserve">14/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabriel Santos</t>
+    <t xml:space="preserve">Fabiano Martins</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
-    <numFmt numFmtId="168" formatCode="#,##0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -333,6 +341,21 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF1B2027"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF1B2027"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="8"/>
       <color rgb="FF6B7784"/>
@@ -341,23 +364,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b val="true"/>
+      <sz val="9.5"/>
       <color rgb="FF1B2027"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF1B2027"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="8.5"/>
-      <color rgb="FF6B7784"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -463,7 +472,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -496,43 +505,59 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -817,13 +842,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -840,7 +870,6 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -856,7 +885,6 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -866,15 +894,14 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
@@ -890,143 +917,136 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="6"/>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="H6" s="6"/>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="6"/>
+      <c r="J6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="7"/>
       <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="6"/>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="H7" s="6"/>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="6"/>
+      <c r="J7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="6"/>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H8" s="6"/>
-      <c r="I8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="7"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="7"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="7"/>
       <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H11" s="6"/>
-      <c r="I11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" s="7"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1038,237 +1058,399 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="6" t="s">
+      <c r="B14" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
+      <c r="D14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>147</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <f aca="false">ROUND(H15*I15*G15,2)</f>
+        <v>28.4</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>147</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <f aca="false">ROUND(H16*I16*G16,2)</f>
+        <v>18</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>147</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <f aca="false">ROUND(H17*I17*G17,2)</f>
+        <v>4.32</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>147</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>96</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <f aca="false">ROUND(H18*I18*G18,2)</f>
+        <v>38.4</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>147</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <f aca="false">ROUND(H19*I19*G19,2)</f>
         <v>33</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="8" t="s">
+      <c r="K19" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>147</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="E20" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="G20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>176</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <f aca="false">ROUND(H20*I20*G20,2)</f>
+        <v>70.4</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>147</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>107</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <f aca="false">ROUND(H21*I21*G21,2)</f>
+        <v>42.8</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>147</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K18" s="9" t="s">
+      <c r="G22" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <f aca="false">ROUND(H22*I22*G22,2)</f>
+        <v>33</v>
+      </c>
+      <c r="K22" s="13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="n">
-        <v>326</v>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>352</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>317</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>344</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>299</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>356</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>347</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>393</v>
-      </c>
-      <c r="I19" s="10" t="n">
-        <v>412</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>356</v>
-      </c>
-      <c r="K19" s="11" t="n">
-        <f aca="false">ROUND(AVERAGE(A19:J19),1)</f>
-        <v>350.2</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="str">
-        <f aca="false">IF(ABS(K19-350.2)&lt;0.05,"Média confere com a declarada no Kartado (350.2)","ATENÇÃO: Kartado declarou 350.2 e as leituras dão "&amp;K19)</f>
-        <v>Média confere com a declarada no Kartado (350.2)</v>
-      </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-    </row>
-    <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
+      <c r="H23" s="16" t="n">
+        <f aca="false">SUM(H15:H22)</f>
+        <v>513.6</v>
+      </c>
+      <c r="I23" s="14"/>
+      <c r="J23" s="17" t="n">
+        <f aca="false">SUM(J15:J22)</f>
+        <v>268.32</v>
+      </c>
+      <c r="K23" s="14"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="G4:L4"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A22:L22"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
+  <mergeCells count="31">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A25:K25"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1285,81 +1467,98 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="13" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="21" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="C1" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="D1" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="E1" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="F1" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="I1" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="J1" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="K1" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="L1" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="M1" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="N1" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="O1" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="P1" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="Q1" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="R1" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="S1" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="T1" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="U1" s="19" t="s">
         <v>67</v>
+      </c>
+      <c r="V1" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="W1" s="19" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1367,63 +1566,529 @@
         <v>2</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="J2" s="7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K2" s="7"/>
       <c r="L2" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="M2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="21" t="n">
+        <v>146</v>
+      </c>
+      <c r="O2" s="21" t="n">
+        <v>147</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="21" t="n">
+        <v>71</v>
+      </c>
+      <c r="U2" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V2" s="21" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="W2" s="7"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="E3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" s="16" t="n">
-        <v>350.2</v>
-      </c>
-      <c r="R2" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="S2" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T2" s="17" t="n">
-        <v>0</v>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="M3" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" s="21" t="n">
+        <v>146</v>
+      </c>
+      <c r="O3" s="21" t="n">
+        <v>147</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="U3" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V3" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="W3" s="7"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="M4" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" s="21" t="n">
+        <v>146</v>
+      </c>
+      <c r="O4" s="21" t="n">
+        <v>147</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U4" s="21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V4" s="21" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="W4" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="M5" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" s="21" t="n">
+        <v>146</v>
+      </c>
+      <c r="O5" s="21" t="n">
+        <v>147</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="S5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="21" t="n">
+        <v>96</v>
+      </c>
+      <c r="U5" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V5" s="21" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="W5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="M6" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" s="21" t="n">
+        <v>146</v>
+      </c>
+      <c r="O6" s="21" t="n">
+        <v>147</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S6" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" s="21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U6" s="21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V6" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="W6" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="M7" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" s="21" t="n">
+        <v>146</v>
+      </c>
+      <c r="O7" s="21" t="n">
+        <v>147</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="S7" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="21" t="n">
+        <v>176</v>
+      </c>
+      <c r="U7" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V7" s="21" t="n">
+        <v>70.4</v>
+      </c>
+      <c r="W7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="M8" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="N8" s="21" t="n">
+        <v>146</v>
+      </c>
+      <c r="O8" s="21" t="n">
+        <v>147</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="S8" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="21" t="n">
+        <v>107</v>
+      </c>
+      <c r="U8" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V8" s="21" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="W8" s="7"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="M9" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="N9" s="21" t="n">
+        <v>146</v>
+      </c>
+      <c r="O9" s="21" t="n">
+        <v>147</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S9" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" s="21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U9" s="21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V9" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="W9" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T2"/>
+  <autoFilter ref="A1:W9"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
